--- a/education_forms/022_long_term_substitute_screening_form--education_forms.xlsx
+++ b/education_forms/022_long_term_substitute_screening_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,7 +1110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -1223,17 +1223,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>education_level_choices</t>
+          <t>role_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>long-term_substitute</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Long-term Substitute</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>long-term_substitute</t>
+          <t>short-term_substitute</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Long-term Substitute</t>
+          <t>Short-term Substitute</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>short-term_substitute</t>
+          <t>emergency_substitute</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Short-term Substitute</t>
+          <t>Emergency Substitute</t>
         </is>
       </c>
     </row>
@@ -1279,63 +1279,63 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>emergency_substitute</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Emergency Substitute</t>
+          <t>None</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>availability_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>monday</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Monday</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>availability_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>tuesday</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Tuesday</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>role_choices</t>
+          <t>availability_choices</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>wednesday</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>Wednesday</t>
         </is>
       </c>
     </row>
@@ -1347,12 +1347,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>monday</t>
+          <t>thursday</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Monday</t>
+          <t>Thursday</t>
         </is>
       </c>
     </row>
@@ -1364,12 +1364,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>tuesday</t>
+          <t>friday</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Tuesday</t>
+          <t>Friday</t>
         </is>
       </c>
     </row>
@@ -1381,12 +1381,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>wednesday</t>
+          <t>saturday</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wednesday</t>
+          <t>Saturday</t>
         </is>
       </c>
     </row>
@@ -1398,12 +1398,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>thursday</t>
+          <t>sunday</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Thursday</t>
+          <t>Sunday</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>friday</t>
+          <t>all</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Friday</t>
+          <t>All</t>
         </is>
       </c>
     </row>
@@ -1432,78 +1432,10 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>saturday</t>
+          <t>none</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
-        <is>
-          <t>Saturday</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>availability_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>sunday</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Sunday</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>availability_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>All</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>availability_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>availability_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>none</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>None</t>
         </is>
